--- a/output/pdf_financials_xlsx/MOG.xlsx
+++ b/output/pdf_financials_xlsx/MOG.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.048475</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.307941</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.384416</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.624088</v>
+        <v>-8.672563</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.597377</v>
+        <v>-6.905318</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-14.377904</v>
+        <v>-14.76232</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.624088</v>
+        <v>-8.672563</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.597377</v>
+        <v>-6.905318</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-14.377904</v>
+        <v>-14.76232</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.398254</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>10.03761</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>18.075804</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.398254</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>10.03761</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5</v>
+        <v>23.075804</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.567271</v>
+        <v>0.169017</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>10.364923</v>
+        <v>0.327313</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>19.292144</v>
+        <v>1.21634</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/MOG.xlsx
+++ b/output/pdf_financials_xlsx/MOG.xlsx
@@ -532,10 +532,10 @@
         <v>0.14314</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.466349</v>
+        <v>0.532349</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.793462</v>
+        <v>0.921462</v>
       </c>
     </row>
     <row r="8">
@@ -580,10 +580,10 @@
         <v>0.5860570000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.004738</v>
+        <v>1.070738</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.254621</v>
+        <v>1.382621</v>
       </c>
     </row>
     <row r="11">
@@ -596,10 +596,10 @@
         <v>-0.5860570000000001</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.004738</v>
+        <v>-1.070738</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.254621</v>
+        <v>-1.382621</v>
       </c>
     </row>
     <row r="12">
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.107941</v>
       </c>
     </row>
     <row r="116">
@@ -3761,7 +3761,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -4530,7 +4534,11 @@
           <t>Directors' fees (note 12)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -4952,7 +4960,11 @@
           <t>Directors' fees (note 10)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
